--- a/excel_files/analytics_dw_xxl.public.dim_vehicle_master.xlsx
+++ b/excel_files/analytics_dw_xxl.public.dim_vehicle_master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PycharmProjects\ETL_Testing_Databricks_Multi_Source\Execution\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A862F0-77D6-42F8-9BD0-72AF01DF5AFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9752BCC4-40B9-451F-9CF0-8CE491D0D2F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6936" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
